--- a/2026/ЗАВОДЫ/ПОКОМ/филиалы НВ/09,26/10,09,26 ПОКОМ ЗПФ/дв 10,09,26 млрсч пок зпф.xlsx
+++ b/2026/ЗАВОДЫ/ПОКОМ/филиалы НВ/09,26/10,09,26 ПОКОМ ЗПФ/дв 10,09,26 млрсч пок зпф.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\расчеты ПОКОМ ЗПФ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Father\Work\2025_05\2026\ЗАВОДЫ\ПОКОМ\филиалы НВ\09,26\10,09,26 ПОКОМ ЗПФ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27771A02-20DC-4826-B8FB-99F66F2528D1}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00FA9FF0-6C33-4E1F-8DAE-43B76E0D405F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,15 +21,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet!$A$3:$AM$74</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="191029" refMode="R1C1"/>
 </workbook>
 </file>
 
@@ -761,7 +753,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Sheet"/>
@@ -1089,7 +1081,8 @@
     <col min="36" max="36" width="6" customWidth="1"/>
     <col min="37" max="38" width="5" customWidth="1"/>
     <col min="39" max="39" width="6" style="12" customWidth="1"/>
-    <col min="40" max="49" width="3" customWidth="1"/>
+    <col min="40" max="40" width="6.7109375" customWidth="1"/>
+    <col min="41" max="49" width="3" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:49" x14ac:dyDescent="0.25">
@@ -1519,7 +1512,10 @@
         <f>SUM(AM6:AM500)</f>
         <v>8.7888888888888879</v>
       </c>
-      <c r="AN5" s="1"/>
+      <c r="AN5" s="4">
+        <f>SUM(AN6:AN500)</f>
+        <v>680.83399999999983</v>
+      </c>
       <c r="AO5" s="1"/>
       <c r="AP5" s="1"/>
       <c r="AQ5" s="1"/>
@@ -1620,7 +1616,10 @@
       <c r="AK6" s="14"/>
       <c r="AL6" s="14"/>
       <c r="AM6" s="17"/>
-      <c r="AN6" s="1"/>
+      <c r="AN6" s="1">
+        <f>P6*G6</f>
+        <v>0</v>
+      </c>
       <c r="AO6" s="1"/>
       <c r="AP6" s="1"/>
       <c r="AQ6" s="1"/>
@@ -1723,7 +1722,10 @@
       <c r="AK7" s="14"/>
       <c r="AL7" s="14"/>
       <c r="AM7" s="17"/>
-      <c r="AN7" s="1"/>
+      <c r="AN7" s="1">
+        <f t="shared" ref="AN7:AN70" si="6">P7*G7</f>
+        <v>0</v>
+      </c>
       <c r="AO7" s="1"/>
       <c r="AP7" s="1"/>
       <c r="AQ7" s="1"/>
@@ -1820,7 +1822,10 @@
       <c r="AK8" s="14"/>
       <c r="AL8" s="14"/>
       <c r="AM8" s="17"/>
-      <c r="AN8" s="1"/>
+      <c r="AN8" s="1">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
       <c r="AO8" s="1"/>
       <c r="AP8" s="1"/>
       <c r="AQ8" s="1"/>
@@ -1917,7 +1922,10 @@
       <c r="AK9" s="14"/>
       <c r="AL9" s="14"/>
       <c r="AM9" s="17"/>
-      <c r="AN9" s="1"/>
+      <c r="AN9" s="1">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
       <c r="AO9" s="1"/>
       <c r="AP9" s="1"/>
       <c r="AQ9" s="1"/>
@@ -2039,7 +2047,10 @@
         <f>AI10/AL10</f>
         <v>0</v>
       </c>
-      <c r="AN10" s="1"/>
+      <c r="AN10" s="1">
+        <f t="shared" si="6"/>
+        <v>0.52800000000000002</v>
+      </c>
       <c r="AO10" s="1"/>
       <c r="AP10" s="1"/>
       <c r="AQ10" s="1"/>
@@ -2164,7 +2175,10 @@
         <f>AI11/AL11</f>
         <v>0</v>
       </c>
-      <c r="AN11" s="1"/>
+      <c r="AN11" s="1">
+        <f t="shared" si="6"/>
+        <v>3.36</v>
+      </c>
       <c r="AO11" s="1"/>
       <c r="AP11" s="1"/>
       <c r="AQ11" s="1"/>
@@ -2265,7 +2279,10 @@
       <c r="AK12" s="14"/>
       <c r="AL12" s="14"/>
       <c r="AM12" s="17"/>
-      <c r="AN12" s="1"/>
+      <c r="AN12" s="1">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
       <c r="AO12" s="1"/>
       <c r="AP12" s="1"/>
       <c r="AQ12" s="1"/>
@@ -2389,7 +2406,10 @@
         <f>AI13/AL13</f>
         <v>0</v>
       </c>
-      <c r="AN13" s="1"/>
+      <c r="AN13" s="1">
+        <f t="shared" si="6"/>
+        <v>5.8240000000000007</v>
+      </c>
       <c r="AO13" s="1"/>
       <c r="AP13" s="1"/>
       <c r="AQ13" s="1"/>
@@ -2515,7 +2535,10 @@
         <f>AI14/AL14</f>
         <v>0</v>
       </c>
-      <c r="AN14" s="1"/>
+      <c r="AN14" s="1">
+        <f t="shared" si="6"/>
+        <v>3.4079999999999999</v>
+      </c>
       <c r="AO14" s="1"/>
       <c r="AP14" s="1"/>
       <c r="AQ14" s="1"/>
@@ -2618,7 +2641,10 @@
       <c r="AK15" s="14"/>
       <c r="AL15" s="14"/>
       <c r="AM15" s="17"/>
-      <c r="AN15" s="1"/>
+      <c r="AN15" s="1">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
       <c r="AO15" s="1"/>
       <c r="AP15" s="1"/>
       <c r="AQ15" s="1"/>
@@ -2677,7 +2703,7 @@
       <c r="Q16" s="5"/>
       <c r="R16" s="5"/>
       <c r="S16" s="5">
-        <f t="shared" ref="S16:S24" si="6">AH16*AI16</f>
+        <f t="shared" ref="S16:S24" si="7">AH16*AI16</f>
         <v>0</v>
       </c>
       <c r="T16" s="1">
@@ -2722,18 +2748,18 @@
         <v>177</v>
       </c>
       <c r="AG16" s="1">
-        <f t="shared" ref="AG16:AG24" si="7">G16*R16</f>
+        <f t="shared" ref="AG16:AG24" si="8">G16*R16</f>
         <v>0</v>
       </c>
       <c r="AH16" s="7">
         <v>12</v>
       </c>
       <c r="AI16" s="9">
-        <f t="shared" ref="AI16:AI24" si="8">MROUND(R16, AH16*AK16)/AH16</f>
+        <f t="shared" ref="AI16:AI24" si="9">MROUND(R16, AH16*AK16)/AH16</f>
         <v>0</v>
       </c>
       <c r="AJ16" s="1">
-        <f t="shared" ref="AJ16:AJ24" si="9">AI16*AH16*G16</f>
+        <f t="shared" ref="AJ16:AJ24" si="10">AI16*AH16*G16</f>
         <v>0</v>
       </c>
       <c r="AK16" s="1">
@@ -2743,10 +2769,13 @@
         <v>70</v>
       </c>
       <c r="AM16" s="9">
-        <f t="shared" ref="AM16:AM24" si="10">AI16/AL16</f>
-        <v>0</v>
-      </c>
-      <c r="AN16" s="1"/>
+        <f t="shared" ref="AM16:AM24" si="11">AI16/AL16</f>
+        <v>0</v>
+      </c>
+      <c r="AN16" s="1">
+        <f t="shared" si="6"/>
+        <v>5.7119999999999997</v>
+      </c>
       <c r="AO16" s="1"/>
       <c r="AP16" s="1"/>
       <c r="AQ16" s="1"/>
@@ -2806,7 +2835,7 @@
         <v>272.8</v>
       </c>
       <c r="S17" s="5">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>336</v>
       </c>
       <c r="T17" s="1">
@@ -2849,18 +2878,18 @@
       </c>
       <c r="AF17" s="1"/>
       <c r="AG17" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>65.471999999999994</v>
       </c>
       <c r="AH17" s="7">
         <v>12</v>
       </c>
       <c r="AI17" s="9">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>28</v>
       </c>
       <c r="AJ17" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>80.64</v>
       </c>
       <c r="AK17" s="1">
@@ -2870,10 +2899,13 @@
         <v>70</v>
       </c>
       <c r="AM17" s="9">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0.4</v>
       </c>
-      <c r="AN17" s="1"/>
+      <c r="AN17" s="1">
+        <f t="shared" si="6"/>
+        <v>5.952</v>
+      </c>
       <c r="AO17" s="1"/>
       <c r="AP17" s="1"/>
       <c r="AQ17" s="1"/>
@@ -2932,7 +2964,7 @@
       <c r="Q18" s="5"/>
       <c r="R18" s="5"/>
       <c r="S18" s="5">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="T18" s="1">
@@ -2975,18 +3007,18 @@
       </c>
       <c r="AF18" s="1"/>
       <c r="AG18" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AH18" s="7">
         <v>12</v>
       </c>
       <c r="AI18" s="9">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AJ18" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AK18" s="1">
@@ -2996,10 +3028,13 @@
         <v>70</v>
       </c>
       <c r="AM18" s="9">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="AN18" s="1"/>
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AN18" s="1">
+        <f t="shared" si="6"/>
+        <v>9.5519999999999996</v>
+      </c>
       <c r="AO18" s="1"/>
       <c r="AP18" s="1"/>
       <c r="AQ18" s="1"/>
@@ -3059,7 +3094,7 @@
         <v>295</v>
       </c>
       <c r="S19" s="5">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>336</v>
       </c>
       <c r="T19" s="1">
@@ -3102,18 +3137,18 @@
       </c>
       <c r="AF19" s="1"/>
       <c r="AG19" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>141.6</v>
       </c>
       <c r="AH19" s="7">
         <v>8</v>
       </c>
       <c r="AI19" s="9">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>42</v>
       </c>
       <c r="AJ19" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>161.28</v>
       </c>
       <c r="AK19" s="1">
@@ -3123,10 +3158,13 @@
         <v>70</v>
       </c>
       <c r="AM19" s="9">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0.6</v>
       </c>
-      <c r="AN19" s="1"/>
+      <c r="AN19" s="1">
+        <f t="shared" si="6"/>
+        <v>14.591999999999999</v>
+      </c>
       <c r="AO19" s="1"/>
       <c r="AP19" s="1"/>
       <c r="AQ19" s="1"/>
@@ -3185,7 +3223,7 @@
         <v>0</v>
       </c>
       <c r="S20" s="20">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="T20" s="1">
@@ -3230,18 +3268,18 @@
         <v>72</v>
       </c>
       <c r="AG20" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AH20" s="7">
         <v>10</v>
       </c>
       <c r="AI20" s="9">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AJ20" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AK20" s="1">
@@ -3251,10 +3289,13 @@
         <v>70</v>
       </c>
       <c r="AM20" s="9">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="AN20" s="1"/>
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AN20" s="1">
+        <f t="shared" si="6"/>
+        <v>4.68</v>
+      </c>
       <c r="AO20" s="1"/>
       <c r="AP20" s="1"/>
       <c r="AQ20" s="1"/>
@@ -3309,7 +3350,7 @@
       <c r="Q21" s="5"/>
       <c r="R21" s="5"/>
       <c r="S21" s="5">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="T21" s="1">
@@ -3352,18 +3393,18 @@
       </c>
       <c r="AF21" s="1"/>
       <c r="AG21" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AH21" s="7">
         <v>12</v>
       </c>
       <c r="AI21" s="9">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AJ21" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AK21" s="1">
@@ -3373,10 +3414,13 @@
         <v>70</v>
       </c>
       <c r="AM21" s="9">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="AN21" s="1"/>
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AN21" s="1">
+        <f t="shared" si="6"/>
+        <v>0.64000000000000012</v>
+      </c>
       <c r="AO21" s="1"/>
       <c r="AP21" s="1"/>
       <c r="AQ21" s="1"/>
@@ -3433,7 +3477,7 @@
       <c r="Q22" s="5"/>
       <c r="R22" s="5"/>
       <c r="S22" s="5">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="T22" s="1">
@@ -3478,18 +3522,18 @@
         <v>77</v>
       </c>
       <c r="AG22" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AH22" s="7">
         <v>12</v>
       </c>
       <c r="AI22" s="9">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AJ22" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AK22" s="1">
@@ -3499,10 +3543,13 @@
         <v>70</v>
       </c>
       <c r="AM22" s="9">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="AN22" s="1"/>
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AN22" s="1">
+        <f t="shared" si="6"/>
+        <v>2.84</v>
+      </c>
       <c r="AO22" s="1"/>
       <c r="AP22" s="1"/>
       <c r="AQ22" s="1"/>
@@ -3558,11 +3605,11 @@
         <v>102.6</v>
       </c>
       <c r="R23" s="5">
-        <f t="shared" ref="R23" si="11">14*P23-F23</f>
+        <f t="shared" ref="R23" si="12">14*P23-F23</f>
         <v>102.6</v>
       </c>
       <c r="S23" s="5">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>168</v>
       </c>
       <c r="T23" s="1">
@@ -3605,18 +3652,18 @@
       </c>
       <c r="AF23" s="1"/>
       <c r="AG23" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>20.52</v>
       </c>
       <c r="AH23" s="7">
         <v>12</v>
       </c>
       <c r="AI23" s="9">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>14</v>
       </c>
       <c r="AJ23" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>33.6</v>
       </c>
       <c r="AK23" s="1">
@@ -3626,10 +3673,13 @@
         <v>70</v>
       </c>
       <c r="AM23" s="9">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0.2</v>
       </c>
-      <c r="AN23" s="1"/>
+      <c r="AN23" s="1">
+        <f t="shared" si="6"/>
+        <v>2.68</v>
+      </c>
       <c r="AO23" s="1"/>
       <c r="AP23" s="1"/>
       <c r="AQ23" s="1"/>
@@ -3687,7 +3737,7 @@
         <v>24.732000000000014</v>
       </c>
       <c r="S24" s="5">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="T24" s="1">
@@ -3730,18 +3780,18 @@
       </c>
       <c r="AF24" s="1"/>
       <c r="AG24" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>24.732000000000014</v>
       </c>
       <c r="AH24" s="7">
         <v>3.7</v>
       </c>
       <c r="AI24" s="9">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AJ24" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AK24" s="1">
@@ -3751,10 +3801,13 @@
         <v>126</v>
       </c>
       <c r="AM24" s="9">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="AN24" s="1"/>
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AN24" s="1">
+        <f t="shared" si="6"/>
+        <v>9.66</v>
+      </c>
       <c r="AO24" s="1"/>
       <c r="AP24" s="1"/>
       <c r="AQ24" s="1"/>
@@ -3853,7 +3906,10 @@
       <c r="AK25" s="14"/>
       <c r="AL25" s="14"/>
       <c r="AM25" s="17"/>
-      <c r="AN25" s="1"/>
+      <c r="AN25" s="1">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
       <c r="AO25" s="1"/>
       <c r="AP25" s="1"/>
       <c r="AQ25" s="1"/>
@@ -3954,7 +4010,10 @@
       <c r="AK26" s="14"/>
       <c r="AL26" s="14"/>
       <c r="AM26" s="17"/>
-      <c r="AN26" s="1"/>
+      <c r="AN26" s="1">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
       <c r="AO26" s="1"/>
       <c r="AP26" s="1"/>
       <c r="AQ26" s="1"/>
@@ -4010,11 +4069,11 @@
         <v>80.3</v>
       </c>
       <c r="R27" s="5">
-        <f t="shared" ref="R27:R71" si="12">14*P27-F27</f>
+        <f t="shared" ref="R27:R51" si="13">14*P27-F27</f>
         <v>80.3</v>
       </c>
       <c r="S27" s="5">
-        <f t="shared" ref="S27:S73" si="13">AH27*AI27</f>
+        <f t="shared" ref="S27:S73" si="14">AH27*AI27</f>
         <v>66</v>
       </c>
       <c r="T27" s="1">
@@ -4057,18 +4116,18 @@
       </c>
       <c r="AF27" s="1"/>
       <c r="AG27" s="1">
-        <f t="shared" ref="AG27:AG73" si="14">G27*R27</f>
+        <f t="shared" ref="AG27:AG73" si="15">G27*R27</f>
         <v>80.3</v>
       </c>
       <c r="AH27" s="7">
         <v>5.5</v>
       </c>
       <c r="AI27" s="9">
-        <f t="shared" ref="AI27:AI73" si="15">MROUND(R27, AH27*AK27)/AH27</f>
+        <f t="shared" ref="AI27:AI73" si="16">MROUND(R27, AH27*AK27)/AH27</f>
         <v>12</v>
       </c>
       <c r="AJ27" s="1">
-        <f t="shared" ref="AJ27:AJ73" si="16">AI27*AH27*G27</f>
+        <f t="shared" ref="AJ27:AJ73" si="17">AI27*AH27*G27</f>
         <v>66</v>
       </c>
       <c r="AK27" s="1">
@@ -4078,10 +4137,13 @@
         <v>84</v>
       </c>
       <c r="AM27" s="9">
-        <f t="shared" ref="AM27:AM73" si="17">AI27/AL27</f>
+        <f t="shared" ref="AM27:AM73" si="18">AI27/AL27</f>
         <v>0.14285714285714285</v>
       </c>
-      <c r="AN27" s="1"/>
+      <c r="AN27" s="1">
+        <f t="shared" si="6"/>
+        <v>7.7</v>
+      </c>
       <c r="AO27" s="1"/>
       <c r="AP27" s="1"/>
       <c r="AQ27" s="1"/>
@@ -4139,11 +4201,11 @@
         <v>69.199999999999989</v>
       </c>
       <c r="R28" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>69.199999999999989</v>
       </c>
       <c r="S28" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>84</v>
       </c>
       <c r="T28" s="1">
@@ -4186,18 +4248,18 @@
       </c>
       <c r="AF28" s="1"/>
       <c r="AG28" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>69.199999999999989</v>
       </c>
       <c r="AH28" s="7">
         <v>3</v>
       </c>
       <c r="AI28" s="9">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>28</v>
       </c>
       <c r="AJ28" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>84</v>
       </c>
       <c r="AK28" s="1">
@@ -4207,10 +4269,13 @@
         <v>126</v>
       </c>
       <c r="AM28" s="9">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0.22222222222222221</v>
       </c>
-      <c r="AN28" s="1"/>
+      <c r="AN28" s="1">
+        <f t="shared" si="6"/>
+        <v>7.2</v>
+      </c>
       <c r="AO28" s="1"/>
       <c r="AP28" s="1"/>
       <c r="AQ28" s="1"/>
@@ -4269,7 +4334,7 @@
       <c r="Q29" s="5"/>
       <c r="R29" s="5"/>
       <c r="S29" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="T29" s="1">
@@ -4312,18 +4377,18 @@
       </c>
       <c r="AF29" s="1"/>
       <c r="AG29" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AH29" s="7">
         <v>6</v>
       </c>
       <c r="AI29" s="9">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AJ29" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AK29" s="1">
@@ -4333,10 +4398,13 @@
         <v>140</v>
       </c>
       <c r="AM29" s="9">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="AN29" s="1"/>
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="AN29" s="1">
+        <f t="shared" si="6"/>
+        <v>10.7</v>
+      </c>
       <c r="AO29" s="1"/>
       <c r="AP29" s="1"/>
       <c r="AQ29" s="1"/>
@@ -4391,7 +4459,7 @@
       <c r="Q30" s="5"/>
       <c r="R30" s="5"/>
       <c r="S30" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="T30" s="1">
@@ -4436,18 +4504,18 @@
         <v>77</v>
       </c>
       <c r="AG30" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AH30" s="7">
         <v>6</v>
       </c>
       <c r="AI30" s="9">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AJ30" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AK30" s="1">
@@ -4457,10 +4525,13 @@
         <v>140</v>
       </c>
       <c r="AM30" s="9">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="AN30" s="1"/>
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="AN30" s="1">
+        <f t="shared" si="6"/>
+        <v>2.4</v>
+      </c>
       <c r="AO30" s="1"/>
       <c r="AP30" s="1"/>
       <c r="AQ30" s="1"/>
@@ -4522,7 +4593,7 @@
         <v>137.95999999999992</v>
       </c>
       <c r="S31" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>144</v>
       </c>
       <c r="T31" s="1">
@@ -4565,18 +4636,18 @@
       </c>
       <c r="AF31" s="1"/>
       <c r="AG31" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>137.95999999999992</v>
       </c>
       <c r="AH31" s="7">
         <v>6</v>
       </c>
       <c r="AI31" s="9">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>24</v>
       </c>
       <c r="AJ31" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>144</v>
       </c>
       <c r="AK31" s="1">
@@ -4586,10 +4657,13 @@
         <v>84</v>
       </c>
       <c r="AM31" s="9">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0.2857142857142857</v>
       </c>
-      <c r="AN31" s="1"/>
+      <c r="AN31" s="1">
+        <f t="shared" si="6"/>
+        <v>34.799999999999997</v>
+      </c>
       <c r="AO31" s="1"/>
       <c r="AP31" s="1"/>
       <c r="AQ31" s="1"/>
@@ -4646,7 +4720,7 @@
       <c r="Q32" s="5"/>
       <c r="R32" s="5"/>
       <c r="S32" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="T32" s="1">
@@ -4689,18 +4763,18 @@
       </c>
       <c r="AF32" s="1"/>
       <c r="AG32" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AH32" s="7">
         <v>12</v>
       </c>
       <c r="AI32" s="9">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AJ32" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AK32" s="1">
@@ -4710,10 +4784,13 @@
         <v>70</v>
       </c>
       <c r="AM32" s="9">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="AN32" s="1"/>
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="AN32" s="1">
+        <f t="shared" si="6"/>
+        <v>1.3340000000000001</v>
+      </c>
       <c r="AO32" s="1"/>
       <c r="AP32" s="1"/>
       <c r="AQ32" s="1"/>
@@ -4770,7 +4847,7 @@
       <c r="Q33" s="5"/>
       <c r="R33" s="5"/>
       <c r="S33" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="T33" s="1">
@@ -4813,18 +4890,18 @@
       </c>
       <c r="AF33" s="1"/>
       <c r="AG33" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AH33" s="7">
         <v>12</v>
       </c>
       <c r="AI33" s="9">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AJ33" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AK33" s="1">
@@ -4834,10 +4911,13 @@
         <v>70</v>
       </c>
       <c r="AM33" s="9">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="AN33" s="1"/>
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="AN33" s="1">
+        <f t="shared" si="6"/>
+        <v>9.25</v>
+      </c>
       <c r="AO33" s="1"/>
       <c r="AP33" s="1"/>
       <c r="AQ33" s="1"/>
@@ -4894,7 +4974,7 @@
       <c r="Q34" s="5"/>
       <c r="R34" s="5"/>
       <c r="S34" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="T34" s="1">
@@ -4937,18 +5017,18 @@
       </c>
       <c r="AF34" s="1"/>
       <c r="AG34" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AH34" s="7">
         <v>12</v>
       </c>
       <c r="AI34" s="9">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AJ34" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AK34" s="1">
@@ -4958,10 +5038,13 @@
         <v>70</v>
       </c>
       <c r="AM34" s="9">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="AN34" s="1"/>
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="AN34" s="1">
+        <f t="shared" si="6"/>
+        <v>12.1</v>
+      </c>
       <c r="AO34" s="1"/>
       <c r="AP34" s="1"/>
       <c r="AQ34" s="1"/>
@@ -5018,7 +5101,7 @@
       <c r="Q35" s="5"/>
       <c r="R35" s="5"/>
       <c r="S35" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="T35" s="1">
@@ -5063,18 +5146,18 @@
         <v>177</v>
       </c>
       <c r="AG35" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AH35" s="7">
         <v>12</v>
       </c>
       <c r="AI35" s="9">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AJ35" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AK35" s="1">
@@ -5084,10 +5167,13 @@
         <v>70</v>
       </c>
       <c r="AM35" s="9">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="AN35" s="1"/>
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="AN35" s="1">
+        <f t="shared" si="6"/>
+        <v>7.95</v>
+      </c>
       <c r="AO35" s="1"/>
       <c r="AP35" s="1"/>
       <c r="AQ35" s="1"/>
@@ -5143,11 +5229,11 @@
         <v>111</v>
       </c>
       <c r="R36" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>111</v>
       </c>
       <c r="S36" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>168</v>
       </c>
       <c r="T36" s="1">
@@ -5190,18 +5276,18 @@
       </c>
       <c r="AF36" s="1"/>
       <c r="AG36" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>27.75</v>
       </c>
       <c r="AH36" s="7">
         <v>12</v>
       </c>
       <c r="AI36" s="9">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>14</v>
       </c>
       <c r="AJ36" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>42</v>
       </c>
       <c r="AK36" s="1">
@@ -5211,10 +5297,13 @@
         <v>70</v>
       </c>
       <c r="AM36" s="9">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0.2</v>
       </c>
-      <c r="AN36" s="1"/>
+      <c r="AN36" s="1">
+        <f t="shared" si="6"/>
+        <v>3</v>
+      </c>
       <c r="AO36" s="1"/>
       <c r="AP36" s="1"/>
       <c r="AQ36" s="1"/>
@@ -5270,11 +5359,11 @@
         <v>98.6</v>
       </c>
       <c r="R37" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>98.6</v>
       </c>
       <c r="S37" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>96</v>
       </c>
       <c r="T37" s="1">
@@ -5317,18 +5406,18 @@
       </c>
       <c r="AF37" s="1"/>
       <c r="AG37" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>69.02</v>
       </c>
       <c r="AH37" s="7">
         <v>8</v>
       </c>
       <c r="AI37" s="9">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>12</v>
       </c>
       <c r="AJ37" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>67.199999999999989</v>
       </c>
       <c r="AK37" s="1">
@@ -5338,10 +5427,13 @@
         <v>84</v>
       </c>
       <c r="AM37" s="9">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0.14285714285714285</v>
       </c>
-      <c r="AN37" s="1"/>
+      <c r="AN37" s="1">
+        <f t="shared" si="6"/>
+        <v>7.2799999999999994</v>
+      </c>
       <c r="AO37" s="1"/>
       <c r="AP37" s="1"/>
       <c r="AQ37" s="1"/>
@@ -5385,14 +5477,14 @@
         <v>49</v>
       </c>
       <c r="L38" s="1">
-        <f t="shared" ref="L38:L69" si="18">E38-K38</f>
+        <f t="shared" ref="L38:L69" si="19">E38-K38</f>
         <v>2</v>
       </c>
       <c r="M38" s="1"/>
       <c r="N38" s="1"/>
       <c r="O38" s="1"/>
       <c r="P38" s="1">
-        <f t="shared" ref="P38:P74" si="19">E38/5</f>
+        <f t="shared" ref="P38:P74" si="20">E38/5</f>
         <v>10.199999999999999</v>
       </c>
       <c r="Q38" s="5"/>
@@ -5401,15 +5493,15 @@
         <v>27.039999999999981</v>
       </c>
       <c r="S38" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="T38" s="1">
-        <f t="shared" ref="T38:T69" si="20">(F38+S38)/P38</f>
+        <f t="shared" ref="T38:T69" si="21">(F38+S38)/P38</f>
         <v>12.549019607843139</v>
       </c>
       <c r="U38" s="1">
-        <f t="shared" ref="U38:U74" si="21">F38/P38</f>
+        <f t="shared" ref="U38:U74" si="22">F38/P38</f>
         <v>12.549019607843139</v>
       </c>
       <c r="V38" s="1">
@@ -5444,18 +5536,18 @@
       </c>
       <c r="AF38" s="1"/>
       <c r="AG38" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>18.927999999999987</v>
       </c>
       <c r="AH38" s="7">
         <v>8</v>
       </c>
       <c r="AI38" s="9">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AJ38" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AK38" s="1">
@@ -5465,10 +5557,13 @@
         <v>84</v>
       </c>
       <c r="AM38" s="9">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="AN38" s="1"/>
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="AN38" s="1">
+        <f t="shared" si="6"/>
+        <v>7.1399999999999988</v>
+      </c>
       <c r="AO38" s="1"/>
       <c r="AP38" s="1"/>
       <c r="AQ38" s="1"/>
@@ -5508,14 +5603,14 @@
         <v>2</v>
       </c>
       <c r="L39" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>-2</v>
       </c>
       <c r="M39" s="1"/>
       <c r="N39" s="1"/>
       <c r="O39" s="1"/>
       <c r="P39" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="Q39" s="20">
@@ -5525,17 +5620,17 @@
         <v>0</v>
       </c>
       <c r="S39" s="20">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="T39" s="1" t="e">
-        <f t="shared" si="20"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U39" s="1" t="e">
         <f t="shared" si="21"/>
         <v>#DIV/0!</v>
       </c>
+      <c r="U39" s="1" t="e">
+        <f t="shared" si="22"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="V39" s="1">
         <v>0</v>
       </c>
@@ -5570,18 +5665,18 @@
         <v>72</v>
       </c>
       <c r="AG39" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AH39" s="7">
         <v>8</v>
       </c>
       <c r="AI39" s="9">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AJ39" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AK39" s="1">
@@ -5591,10 +5686,13 @@
         <v>84</v>
       </c>
       <c r="AM39" s="9">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="AN39" s="1"/>
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="AN39" s="1">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
       <c r="AO39" s="1"/>
       <c r="AP39" s="1"/>
       <c r="AQ39" s="1"/>
@@ -5638,30 +5736,30 @@
         <v>76</v>
       </c>
       <c r="L40" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="M40" s="1"/>
       <c r="N40" s="1"/>
       <c r="O40" s="1"/>
       <c r="P40" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>15.4</v>
       </c>
       <c r="Q40" s="5"/>
       <c r="R40" s="5"/>
       <c r="S40" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="T40" s="1">
-        <f t="shared" si="20"/>
-        <v>30.714285714285715</v>
-      </c>
-      <c r="U40" s="1">
         <f t="shared" si="21"/>
         <v>30.714285714285715</v>
       </c>
+      <c r="U40" s="1">
+        <f t="shared" si="22"/>
+        <v>30.714285714285715</v>
+      </c>
       <c r="V40" s="1">
         <v>27.8</v>
       </c>
@@ -5696,18 +5794,18 @@
         <v>77</v>
       </c>
       <c r="AG40" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AH40" s="7">
         <v>10</v>
       </c>
       <c r="AI40" s="9">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AJ40" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AK40" s="1">
@@ -5717,10 +5815,13 @@
         <v>84</v>
       </c>
       <c r="AM40" s="9">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="AN40" s="1"/>
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="AN40" s="1">
+        <f t="shared" si="6"/>
+        <v>10.78</v>
+      </c>
       <c r="AO40" s="1"/>
       <c r="AP40" s="1"/>
       <c r="AQ40" s="1"/>
@@ -5762,30 +5863,30 @@
         <v>55</v>
       </c>
       <c r="L41" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>-1</v>
       </c>
       <c r="M41" s="1"/>
       <c r="N41" s="1"/>
       <c r="O41" s="1"/>
       <c r="P41" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>10.8</v>
       </c>
       <c r="Q41" s="5"/>
       <c r="R41" s="5"/>
       <c r="S41" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="T41" s="1">
-        <f t="shared" si="20"/>
-        <v>21.481481481481481</v>
-      </c>
-      <c r="U41" s="1">
         <f t="shared" si="21"/>
         <v>21.481481481481481</v>
       </c>
+      <c r="U41" s="1">
+        <f t="shared" si="22"/>
+        <v>21.481481481481481</v>
+      </c>
       <c r="V41" s="1">
         <v>5.6</v>
       </c>
@@ -5820,18 +5921,18 @@
         <v>77</v>
       </c>
       <c r="AG41" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AH41" s="7">
         <v>10</v>
       </c>
       <c r="AI41" s="9">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AJ41" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AK41" s="1">
@@ -5841,10 +5942,13 @@
         <v>84</v>
       </c>
       <c r="AM41" s="9">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="AN41" s="1"/>
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="AN41" s="1">
+        <f t="shared" si="6"/>
+        <v>7.56</v>
+      </c>
       <c r="AO41" s="1"/>
       <c r="AP41" s="1"/>
       <c r="AQ41" s="1"/>
@@ -5886,30 +5990,30 @@
         <v>55</v>
       </c>
       <c r="L42" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>6</v>
       </c>
       <c r="M42" s="1"/>
       <c r="N42" s="1"/>
       <c r="O42" s="1"/>
       <c r="P42" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>12.2</v>
       </c>
       <c r="Q42" s="5"/>
       <c r="R42" s="5"/>
       <c r="S42" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="T42" s="1">
-        <f t="shared" si="20"/>
-        <v>30.983606557377051</v>
-      </c>
-      <c r="U42" s="1">
         <f t="shared" si="21"/>
         <v>30.983606557377051</v>
       </c>
+      <c r="U42" s="1">
+        <f t="shared" si="22"/>
+        <v>30.983606557377051</v>
+      </c>
       <c r="V42" s="1">
         <v>23</v>
       </c>
@@ -5944,18 +6048,18 @@
         <v>77</v>
       </c>
       <c r="AG42" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AH42" s="7">
         <v>10</v>
       </c>
       <c r="AI42" s="9">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AJ42" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AK42" s="1">
@@ -5965,10 +6069,13 @@
         <v>84</v>
       </c>
       <c r="AM42" s="9">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="AN42" s="1"/>
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="AN42" s="1">
+        <f t="shared" si="6"/>
+        <v>8.5399999999999991</v>
+      </c>
       <c r="AO42" s="1"/>
       <c r="AP42" s="1"/>
       <c r="AQ42" s="1"/>
@@ -6010,30 +6117,30 @@
         <v>40</v>
       </c>
       <c r="L43" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="M43" s="1"/>
       <c r="N43" s="1"/>
       <c r="O43" s="1"/>
       <c r="P43" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>8</v>
       </c>
       <c r="Q43" s="5"/>
       <c r="R43" s="5"/>
       <c r="S43" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="T43" s="1">
-        <f t="shared" si="20"/>
-        <v>23.125</v>
-      </c>
-      <c r="U43" s="1">
         <f t="shared" si="21"/>
         <v>23.125</v>
       </c>
+      <c r="U43" s="1">
+        <f t="shared" si="22"/>
+        <v>23.125</v>
+      </c>
       <c r="V43" s="1">
         <v>20.399999999999999</v>
       </c>
@@ -6066,18 +6173,18 @@
       </c>
       <c r="AF43" s="1"/>
       <c r="AG43" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AH43" s="7">
         <v>10</v>
       </c>
       <c r="AI43" s="9">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AJ43" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AK43" s="1">
@@ -6087,10 +6194,13 @@
         <v>84</v>
       </c>
       <c r="AM43" s="9">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="AN43" s="1"/>
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="AN43" s="1">
+        <f t="shared" si="6"/>
+        <v>5.6</v>
+      </c>
       <c r="AO43" s="1"/>
       <c r="AP43" s="1"/>
       <c r="AQ43" s="1"/>
@@ -6134,14 +6244,14 @@
         <v>310</v>
       </c>
       <c r="L44" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>-15</v>
       </c>
       <c r="M44" s="1"/>
       <c r="N44" s="1"/>
       <c r="O44" s="1"/>
       <c r="P44" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>59</v>
       </c>
       <c r="Q44" s="5">
@@ -6152,15 +6262,15 @@
         <v>496.8</v>
       </c>
       <c r="S44" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>480</v>
       </c>
       <c r="T44" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>14.915254237288135</v>
       </c>
       <c r="U44" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>6.7796610169491522</v>
       </c>
       <c r="V44" s="1">
@@ -6195,18 +6305,18 @@
       </c>
       <c r="AF44" s="1"/>
       <c r="AG44" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>496.8</v>
       </c>
       <c r="AH44" s="7">
         <v>5</v>
       </c>
       <c r="AI44" s="9">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>96</v>
       </c>
       <c r="AJ44" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>480</v>
       </c>
       <c r="AK44" s="1">
@@ -6216,10 +6326,13 @@
         <v>144</v>
       </c>
       <c r="AM44" s="9">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0.66666666666666663</v>
       </c>
-      <c r="AN44" s="1"/>
+      <c r="AN44" s="1">
+        <f t="shared" si="6"/>
+        <v>59</v>
+      </c>
       <c r="AO44" s="1"/>
       <c r="AP44" s="1"/>
       <c r="AQ44" s="1"/>
@@ -6261,30 +6374,30 @@
         <v>47</v>
       </c>
       <c r="L45" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="M45" s="1"/>
       <c r="N45" s="1"/>
       <c r="O45" s="1"/>
       <c r="P45" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>9.4</v>
       </c>
       <c r="Q45" s="5"/>
       <c r="R45" s="5"/>
       <c r="S45" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="T45" s="1">
-        <f t="shared" si="20"/>
-        <v>38.191489361702125</v>
-      </c>
-      <c r="U45" s="1">
         <f t="shared" si="21"/>
         <v>38.191489361702125</v>
       </c>
+      <c r="U45" s="1">
+        <f t="shared" si="22"/>
+        <v>38.191489361702125</v>
+      </c>
       <c r="V45" s="1">
         <v>26.8</v>
       </c>
@@ -6319,18 +6432,18 @@
         <v>77</v>
       </c>
       <c r="AG45" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AH45" s="7">
         <v>16</v>
       </c>
       <c r="AI45" s="9">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AJ45" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AK45" s="1">
@@ -6340,10 +6453,13 @@
         <v>84</v>
       </c>
       <c r="AM45" s="9">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="AN45" s="1"/>
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="AN45" s="1">
+        <f t="shared" si="6"/>
+        <v>3.7600000000000002</v>
+      </c>
       <c r="AO45" s="1"/>
       <c r="AP45" s="1"/>
       <c r="AQ45" s="1"/>
@@ -6387,30 +6503,30 @@
         <v>132</v>
       </c>
       <c r="L46" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>-5</v>
       </c>
       <c r="M46" s="1"/>
       <c r="N46" s="1"/>
       <c r="O46" s="1"/>
       <c r="P46" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>25.4</v>
       </c>
       <c r="Q46" s="5"/>
       <c r="R46" s="5"/>
       <c r="S46" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="T46" s="1">
-        <f t="shared" si="20"/>
-        <v>17.677165354330711</v>
-      </c>
-      <c r="U46" s="1">
         <f t="shared" si="21"/>
         <v>17.677165354330711</v>
       </c>
+      <c r="U46" s="1">
+        <f t="shared" si="22"/>
+        <v>17.677165354330711</v>
+      </c>
       <c r="V46" s="1">
         <v>49.4</v>
       </c>
@@ -6443,18 +6559,18 @@
       </c>
       <c r="AF46" s="1"/>
       <c r="AG46" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AH46" s="7">
         <v>10</v>
       </c>
       <c r="AI46" s="9">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AJ46" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AK46" s="1">
@@ -6464,10 +6580,13 @@
         <v>84</v>
       </c>
       <c r="AM46" s="9">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="AN46" s="1"/>
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="AN46" s="1">
+        <f t="shared" si="6"/>
+        <v>17.779999999999998</v>
+      </c>
       <c r="AO46" s="1"/>
       <c r="AP46" s="1"/>
       <c r="AQ46" s="1"/>
@@ -6511,30 +6630,30 @@
         <v>80</v>
       </c>
       <c r="L47" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>6</v>
       </c>
       <c r="M47" s="1"/>
       <c r="N47" s="1"/>
       <c r="O47" s="1"/>
       <c r="P47" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>17.2</v>
       </c>
       <c r="Q47" s="5"/>
       <c r="R47" s="5"/>
       <c r="S47" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="T47" s="1">
-        <f t="shared" si="20"/>
-        <v>45.465116279069768</v>
-      </c>
-      <c r="U47" s="1">
         <f t="shared" si="21"/>
         <v>45.465116279069768</v>
       </c>
+      <c r="U47" s="1">
+        <f t="shared" si="22"/>
+        <v>45.465116279069768</v>
+      </c>
       <c r="V47" s="1">
         <v>42.4</v>
       </c>
@@ -6569,18 +6688,18 @@
         <v>77</v>
       </c>
       <c r="AG47" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AH47" s="7">
         <v>16</v>
       </c>
       <c r="AI47" s="9">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AJ47" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AK47" s="1">
@@ -6590,10 +6709,13 @@
         <v>84</v>
       </c>
       <c r="AM47" s="9">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="AN47" s="1"/>
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="AN47" s="1">
+        <f t="shared" si="6"/>
+        <v>6.88</v>
+      </c>
       <c r="AO47" s="1"/>
       <c r="AP47" s="1"/>
       <c r="AQ47" s="1"/>
@@ -6638,14 +6760,14 @@
         <v>332</v>
       </c>
       <c r="L48" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>6</v>
       </c>
       <c r="M48" s="1"/>
       <c r="N48" s="1"/>
       <c r="O48" s="1"/>
       <c r="P48" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>67.599999999999994</v>
       </c>
       <c r="Q48" s="5">
@@ -6656,15 +6778,15 @@
         <v>583.51999999999987</v>
       </c>
       <c r="S48" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>600</v>
       </c>
       <c r="T48" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>15.443786982248522</v>
       </c>
       <c r="U48" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>6.5680473372781067</v>
       </c>
       <c r="V48" s="1">
@@ -6699,18 +6821,18 @@
       </c>
       <c r="AF48" s="1"/>
       <c r="AG48" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>408.46399999999988</v>
       </c>
       <c r="AH48" s="7">
         <v>10</v>
       </c>
       <c r="AI48" s="9">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>60</v>
       </c>
       <c r="AJ48" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>420</v>
       </c>
       <c r="AK48" s="1">
@@ -6720,10 +6842,13 @@
         <v>84</v>
       </c>
       <c r="AM48" s="9">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0.7142857142857143</v>
       </c>
-      <c r="AN48" s="1"/>
+      <c r="AN48" s="1">
+        <f t="shared" si="6"/>
+        <v>47.319999999999993</v>
+      </c>
       <c r="AO48" s="1"/>
       <c r="AP48" s="1"/>
       <c r="AQ48" s="1"/>
@@ -6767,14 +6892,14 @@
         <v>54</v>
       </c>
       <c r="L49" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="M49" s="1"/>
       <c r="N49" s="1"/>
       <c r="O49" s="1"/>
       <c r="P49" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>10.8</v>
       </c>
       <c r="Q49" s="5">
@@ -6785,15 +6910,15 @@
         <v>64.800000000000011</v>
       </c>
       <c r="S49" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>120</v>
       </c>
       <c r="T49" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>21.111111111111111</v>
       </c>
       <c r="U49" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>10</v>
       </c>
       <c r="V49" s="1">
@@ -6828,18 +6953,18 @@
       </c>
       <c r="AF49" s="1"/>
       <c r="AG49" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>45.360000000000007</v>
       </c>
       <c r="AH49" s="7">
         <v>10</v>
       </c>
       <c r="AI49" s="9">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>12</v>
       </c>
       <c r="AJ49" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>84</v>
       </c>
       <c r="AK49" s="1">
@@ -6849,10 +6974,13 @@
         <v>84</v>
       </c>
       <c r="AM49" s="9">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0.14285714285714285</v>
       </c>
-      <c r="AN49" s="1"/>
+      <c r="AN49" s="1">
+        <f t="shared" si="6"/>
+        <v>7.56</v>
+      </c>
       <c r="AO49" s="1"/>
       <c r="AP49" s="1"/>
       <c r="AQ49" s="1"/>
@@ -6896,14 +7024,14 @@
         <v>229</v>
       </c>
       <c r="L50" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>-47</v>
       </c>
       <c r="M50" s="1"/>
       <c r="N50" s="1"/>
       <c r="O50" s="1"/>
       <c r="P50" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>36.4</v>
       </c>
       <c r="Q50" s="5">
@@ -6914,15 +7042,15 @@
         <v>356</v>
       </c>
       <c r="S50" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>384</v>
       </c>
       <c r="T50" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>10.76923076923077</v>
       </c>
       <c r="U50" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0.21978021978021978</v>
       </c>
       <c r="V50" s="1">
@@ -6957,18 +7085,18 @@
       </c>
       <c r="AF50" s="1"/>
       <c r="AG50" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>284.8</v>
       </c>
       <c r="AH50" s="7">
         <v>8</v>
       </c>
       <c r="AI50" s="9">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>48</v>
       </c>
       <c r="AJ50" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>307.20000000000005</v>
       </c>
       <c r="AK50" s="1">
@@ -6978,10 +7106,13 @@
         <v>84</v>
       </c>
       <c r="AM50" s="9">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0.5714285714285714</v>
       </c>
-      <c r="AN50" s="1"/>
+      <c r="AN50" s="1">
+        <f t="shared" si="6"/>
+        <v>29.12</v>
+      </c>
       <c r="AO50" s="1"/>
       <c r="AP50" s="1"/>
       <c r="AQ50" s="1"/>
@@ -7025,33 +7156,33 @@
         <v>163</v>
       </c>
       <c r="L51" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>9</v>
       </c>
       <c r="M51" s="1"/>
       <c r="N51" s="1"/>
       <c r="O51" s="1"/>
       <c r="P51" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>34.4</v>
       </c>
       <c r="Q51" s="5">
         <v>324.59999999999997</v>
       </c>
       <c r="R51" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>324.59999999999997</v>
       </c>
       <c r="S51" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>300</v>
       </c>
       <c r="T51" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>13.284883720930234</v>
       </c>
       <c r="U51" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>4.5639534883720936</v>
       </c>
       <c r="V51" s="1">
@@ -7086,18 +7217,18 @@
       </c>
       <c r="AF51" s="1"/>
       <c r="AG51" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>324.59999999999997</v>
       </c>
       <c r="AH51" s="7">
         <v>5</v>
       </c>
       <c r="AI51" s="9">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>60</v>
       </c>
       <c r="AJ51" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>300</v>
       </c>
       <c r="AK51" s="1">
@@ -7107,10 +7238,13 @@
         <v>84</v>
       </c>
       <c r="AM51" s="9">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0.7142857142857143</v>
       </c>
-      <c r="AN51" s="1"/>
+      <c r="AN51" s="1">
+        <f t="shared" si="6"/>
+        <v>34.4</v>
+      </c>
       <c r="AO51" s="1"/>
       <c r="AP51" s="1"/>
       <c r="AQ51" s="1"/>
@@ -7154,14 +7288,14 @@
         <v>80</v>
       </c>
       <c r="L52" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>9</v>
       </c>
       <c r="M52" s="1"/>
       <c r="N52" s="1"/>
       <c r="O52" s="1"/>
       <c r="P52" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>17.8</v>
       </c>
       <c r="Q52" s="5"/>
@@ -7170,17 +7304,17 @@
         <v>0</v>
       </c>
       <c r="S52" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="T52" s="1">
-        <f t="shared" si="20"/>
-        <v>15.393258426966291</v>
-      </c>
-      <c r="U52" s="1">
         <f t="shared" si="21"/>
         <v>15.393258426966291</v>
       </c>
+      <c r="U52" s="1">
+        <f t="shared" si="22"/>
+        <v>15.393258426966291</v>
+      </c>
       <c r="V52" s="1">
         <v>19.8</v>
       </c>
@@ -7213,18 +7347,18 @@
       </c>
       <c r="AF52" s="1"/>
       <c r="AG52" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AH52" s="7">
         <v>8</v>
       </c>
       <c r="AI52" s="9">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AJ52" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AK52" s="1">
@@ -7234,10 +7368,13 @@
         <v>84</v>
       </c>
       <c r="AM52" s="9">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="AN52" s="1"/>
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="AN52" s="1">
+        <f t="shared" si="6"/>
+        <v>16.02</v>
+      </c>
       <c r="AO52" s="1"/>
       <c r="AP52" s="1"/>
       <c r="AQ52" s="1"/>
@@ -7281,30 +7418,30 @@
         <v>41</v>
       </c>
       <c r="L53" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>-5</v>
       </c>
       <c r="M53" s="1"/>
       <c r="N53" s="1"/>
       <c r="O53" s="1"/>
       <c r="P53" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>7.2</v>
       </c>
       <c r="Q53" s="5"/>
       <c r="R53" s="5"/>
       <c r="S53" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="T53" s="1">
-        <f t="shared" si="20"/>
-        <v>46.388888888888886</v>
-      </c>
-      <c r="U53" s="1">
         <f t="shared" si="21"/>
         <v>46.388888888888886</v>
       </c>
+      <c r="U53" s="1">
+        <f t="shared" si="22"/>
+        <v>46.388888888888886</v>
+      </c>
       <c r="V53" s="1">
         <v>19.600000000000001</v>
       </c>
@@ -7339,18 +7476,18 @@
         <v>77</v>
       </c>
       <c r="AG53" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AH53" s="7">
         <v>8</v>
       </c>
       <c r="AI53" s="9">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AJ53" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AK53" s="1">
@@ -7360,10 +7497,13 @@
         <v>84</v>
       </c>
       <c r="AM53" s="9">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="AN53" s="1"/>
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="AN53" s="1">
+        <f t="shared" si="6"/>
+        <v>6.48</v>
+      </c>
       <c r="AO53" s="1"/>
       <c r="AP53" s="1"/>
       <c r="AQ53" s="1"/>
@@ -7407,30 +7547,30 @@
         <v>50</v>
       </c>
       <c r="L54" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>-5</v>
       </c>
       <c r="M54" s="1"/>
       <c r="N54" s="1"/>
       <c r="O54" s="1"/>
       <c r="P54" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>9</v>
       </c>
       <c r="Q54" s="5"/>
       <c r="R54" s="5"/>
       <c r="S54" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="T54" s="1">
-        <f t="shared" si="20"/>
-        <v>27.777777777777779</v>
-      </c>
-      <c r="U54" s="1">
         <f t="shared" si="21"/>
         <v>27.777777777777779</v>
       </c>
+      <c r="U54" s="1">
+        <f t="shared" si="22"/>
+        <v>27.777777777777779</v>
+      </c>
       <c r="V54" s="1">
         <v>11</v>
       </c>
@@ -7465,18 +7605,18 @@
         <v>177</v>
       </c>
       <c r="AG54" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AH54" s="7">
         <v>5</v>
       </c>
       <c r="AI54" s="9">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AJ54" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AK54" s="1">
@@ -7486,10 +7626,13 @@
         <v>144</v>
       </c>
       <c r="AM54" s="9">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="AN54" s="1"/>
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="AN54" s="1">
+        <f t="shared" si="6"/>
+        <v>9</v>
+      </c>
       <c r="AO54" s="1"/>
       <c r="AP54" s="1"/>
       <c r="AQ54" s="1"/>
@@ -7533,14 +7676,14 @@
         <v>330</v>
       </c>
       <c r="L55" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>19</v>
       </c>
       <c r="M55" s="1"/>
       <c r="N55" s="1"/>
       <c r="O55" s="1"/>
       <c r="P55" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>69.8</v>
       </c>
       <c r="Q55" s="5">
@@ -7551,15 +7694,15 @@
         <v>719.4</v>
       </c>
       <c r="S55" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>720</v>
       </c>
       <c r="T55" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>13.008595988538682</v>
       </c>
       <c r="U55" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>2.6934097421203438</v>
       </c>
       <c r="V55" s="1">
@@ -7594,18 +7737,18 @@
       </c>
       <c r="AF55" s="1"/>
       <c r="AG55" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>719.4</v>
       </c>
       <c r="AH55" s="7">
         <v>5</v>
       </c>
       <c r="AI55" s="9">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>144</v>
       </c>
       <c r="AJ55" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>720</v>
       </c>
       <c r="AK55" s="1">
@@ -7615,10 +7758,13 @@
         <v>84</v>
       </c>
       <c r="AM55" s="9">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>1.7142857142857142</v>
       </c>
-      <c r="AN55" s="1"/>
+      <c r="AN55" s="1">
+        <f t="shared" si="6"/>
+        <v>69.8</v>
+      </c>
       <c r="AO55" s="1"/>
       <c r="AP55" s="1"/>
       <c r="AQ55" s="1"/>
@@ -7660,30 +7806,30 @@
         <v>18.5</v>
       </c>
       <c r="L56" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="M56" s="1"/>
       <c r="N56" s="1"/>
       <c r="O56" s="1"/>
       <c r="P56" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>3.7</v>
       </c>
       <c r="Q56" s="5"/>
       <c r="R56" s="5"/>
       <c r="S56" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="T56" s="1">
-        <f t="shared" si="20"/>
-        <v>55.999999999999993</v>
-      </c>
-      <c r="U56" s="1">
         <f t="shared" si="21"/>
         <v>55.999999999999993</v>
       </c>
+      <c r="U56" s="1">
+        <f t="shared" si="22"/>
+        <v>55.999999999999993</v>
+      </c>
       <c r="V56" s="1">
         <v>0</v>
       </c>
@@ -7718,18 +7864,18 @@
         <v>77</v>
       </c>
       <c r="AG56" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AH56" s="7">
         <v>3.7</v>
       </c>
       <c r="AI56" s="9">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AJ56" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AK56" s="1">
@@ -7739,10 +7885,13 @@
         <v>126</v>
       </c>
       <c r="AM56" s="9">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="AN56" s="1"/>
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="AN56" s="1">
+        <f t="shared" si="6"/>
+        <v>3.7</v>
+      </c>
       <c r="AO56" s="1"/>
       <c r="AP56" s="1"/>
       <c r="AQ56" s="1"/>
@@ -7784,30 +7933,30 @@
         <v>25</v>
       </c>
       <c r="L57" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>2</v>
       </c>
       <c r="M57" s="1"/>
       <c r="N57" s="1"/>
       <c r="O57" s="1"/>
       <c r="P57" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>5.4</v>
       </c>
       <c r="Q57" s="5"/>
       <c r="R57" s="5"/>
       <c r="S57" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="T57" s="1">
-        <f t="shared" si="20"/>
-        <v>18.703703703703702</v>
-      </c>
-      <c r="U57" s="1">
         <f t="shared" si="21"/>
         <v>18.703703703703702</v>
       </c>
+      <c r="U57" s="1">
+        <f t="shared" si="22"/>
+        <v>18.703703703703702</v>
+      </c>
       <c r="V57" s="1">
         <v>9</v>
       </c>
@@ -7840,18 +7989,18 @@
       </c>
       <c r="AF57" s="1"/>
       <c r="AG57" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AH57" s="7">
         <v>6</v>
       </c>
       <c r="AI57" s="9">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AJ57" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AK57" s="1">
@@ -7861,10 +8010,13 @@
         <v>140</v>
       </c>
       <c r="AM57" s="9">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="AN57" s="1"/>
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="AN57" s="1">
+        <f t="shared" si="6"/>
+        <v>1.2420000000000002</v>
+      </c>
       <c r="AO57" s="1"/>
       <c r="AP57" s="1"/>
       <c r="AQ57" s="1"/>
@@ -7907,30 +8059,30 @@
         <v>201</v>
       </c>
       <c r="L58" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="M58" s="1"/>
       <c r="N58" s="1"/>
       <c r="O58" s="1"/>
       <c r="P58" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>40.4</v>
       </c>
       <c r="Q58" s="5"/>
       <c r="R58" s="5"/>
       <c r="S58" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="T58" s="1">
-        <f t="shared" si="20"/>
-        <v>15.544554455445546</v>
-      </c>
-      <c r="U58" s="1">
         <f t="shared" si="21"/>
         <v>15.544554455445546</v>
       </c>
+      <c r="U58" s="1">
+        <f t="shared" si="22"/>
+        <v>15.544554455445546</v>
+      </c>
       <c r="V58" s="1">
         <v>51.4</v>
       </c>
@@ -7963,18 +8115,18 @@
       </c>
       <c r="AF58" s="1"/>
       <c r="AG58" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AH58" s="7">
         <v>12</v>
       </c>
       <c r="AI58" s="9">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AJ58" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AK58" s="1">
@@ -7984,10 +8136,13 @@
         <v>70</v>
       </c>
       <c r="AM58" s="9">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="AN58" s="1"/>
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="AN58" s="1">
+        <f t="shared" si="6"/>
+        <v>10.1</v>
+      </c>
       <c r="AO58" s="1"/>
       <c r="AP58" s="1"/>
       <c r="AQ58" s="1"/>
@@ -8029,14 +8184,14 @@
         <v>88</v>
       </c>
       <c r="L59" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="M59" s="1"/>
       <c r="N59" s="1"/>
       <c r="O59" s="1"/>
       <c r="P59" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>17.8</v>
       </c>
       <c r="Q59" s="5">
@@ -8047,15 +8202,15 @@
         <v>91.800000000000011</v>
       </c>
       <c r="S59" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>168</v>
       </c>
       <c r="T59" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>20.280898876404493</v>
       </c>
       <c r="U59" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>10.842696629213483</v>
       </c>
       <c r="V59" s="1">
@@ -8090,18 +8245,18 @@
       </c>
       <c r="AF59" s="1"/>
       <c r="AG59" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>22.950000000000003</v>
       </c>
       <c r="AH59" s="7">
         <v>12</v>
       </c>
       <c r="AI59" s="9">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>14</v>
       </c>
       <c r="AJ59" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>42</v>
       </c>
       <c r="AK59" s="1">
@@ -8111,10 +8266,13 @@
         <v>70</v>
       </c>
       <c r="AM59" s="9">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0.2</v>
       </c>
-      <c r="AN59" s="1"/>
+      <c r="AN59" s="1">
+        <f t="shared" si="6"/>
+        <v>4.45</v>
+      </c>
       <c r="AO59" s="1"/>
       <c r="AP59" s="1"/>
       <c r="AQ59" s="1"/>
@@ -8156,30 +8314,30 @@
         <v>6</v>
       </c>
       <c r="L60" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="M60" s="1"/>
       <c r="N60" s="1"/>
       <c r="O60" s="1"/>
       <c r="P60" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1.2</v>
       </c>
       <c r="Q60" s="5"/>
       <c r="R60" s="5"/>
       <c r="S60" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="T60" s="1">
-        <f t="shared" si="20"/>
-        <v>165.83333333333334</v>
-      </c>
-      <c r="U60" s="1">
         <f t="shared" si="21"/>
         <v>165.83333333333334</v>
       </c>
+      <c r="U60" s="1">
+        <f t="shared" si="22"/>
+        <v>165.83333333333334</v>
+      </c>
       <c r="V60" s="1">
         <v>0</v>
       </c>
@@ -8214,18 +8372,18 @@
         <v>77</v>
       </c>
       <c r="AG60" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AH60" s="7">
         <v>6</v>
       </c>
       <c r="AI60" s="9">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AJ60" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AK60" s="1">
@@ -8235,10 +8393,13 @@
         <v>140</v>
       </c>
       <c r="AM60" s="9">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="AN60" s="1"/>
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="AN60" s="1">
+        <f t="shared" si="6"/>
+        <v>0.216</v>
+      </c>
       <c r="AO60" s="1"/>
       <c r="AP60" s="1"/>
       <c r="AQ60" s="1"/>
@@ -8276,30 +8437,30 @@
       <c r="J61" s="1"/>
       <c r="K61" s="1"/>
       <c r="L61" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="M61" s="1"/>
       <c r="N61" s="1"/>
       <c r="O61" s="1"/>
       <c r="P61" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="Q61" s="5"/>
       <c r="R61" s="5"/>
       <c r="S61" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="T61" s="1" t="e">
-        <f t="shared" si="20"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U61" s="1" t="e">
         <f t="shared" si="21"/>
         <v>#DIV/0!</v>
       </c>
+      <c r="U61" s="1" t="e">
+        <f t="shared" si="22"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="V61" s="1">
         <v>0</v>
       </c>
@@ -8334,18 +8495,18 @@
         <v>77</v>
       </c>
       <c r="AG61" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AH61" s="7">
         <v>6</v>
       </c>
       <c r="AI61" s="9">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AJ61" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AK61" s="1">
@@ -8355,10 +8516,13 @@
         <v>140</v>
       </c>
       <c r="AM61" s="9">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="AN61" s="1"/>
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="AN61" s="1">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
       <c r="AO61" s="1"/>
       <c r="AP61" s="1"/>
       <c r="AQ61" s="1"/>
@@ -8396,30 +8560,30 @@
       <c r="J62" s="1"/>
       <c r="K62" s="1"/>
       <c r="L62" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="M62" s="1"/>
       <c r="N62" s="1"/>
       <c r="O62" s="1"/>
       <c r="P62" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="Q62" s="5"/>
       <c r="R62" s="5"/>
       <c r="S62" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="T62" s="1" t="e">
-        <f t="shared" si="20"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U62" s="1" t="e">
         <f t="shared" si="21"/>
         <v>#DIV/0!</v>
       </c>
+      <c r="U62" s="1" t="e">
+        <f t="shared" si="22"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="V62" s="1">
         <v>0</v>
       </c>
@@ -8454,18 +8618,18 @@
         <v>77</v>
       </c>
       <c r="AG62" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AH62" s="7">
         <v>6</v>
       </c>
       <c r="AI62" s="9">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AJ62" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AK62" s="1">
@@ -8475,10 +8639,13 @@
         <v>140</v>
       </c>
       <c r="AM62" s="9">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="AN62" s="1"/>
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="AN62" s="1">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
       <c r="AO62" s="1"/>
       <c r="AP62" s="1"/>
       <c r="AQ62" s="1"/>
@@ -8522,30 +8689,30 @@
         <v>208</v>
       </c>
       <c r="L63" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>3</v>
       </c>
       <c r="M63" s="1"/>
       <c r="N63" s="1"/>
       <c r="O63" s="1"/>
       <c r="P63" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>42.2</v>
       </c>
       <c r="Q63" s="5"/>
       <c r="R63" s="5"/>
       <c r="S63" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="T63" s="1">
-        <f t="shared" si="20"/>
-        <v>16.611374407582936</v>
-      </c>
-      <c r="U63" s="1">
         <f t="shared" si="21"/>
         <v>16.611374407582936</v>
       </c>
+      <c r="U63" s="1">
+        <f t="shared" si="22"/>
+        <v>16.611374407582936</v>
+      </c>
       <c r="V63" s="1">
         <v>19</v>
       </c>
@@ -8578,18 +8745,18 @@
       </c>
       <c r="AF63" s="1"/>
       <c r="AG63" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AH63" s="7">
         <v>12</v>
       </c>
       <c r="AI63" s="9">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AJ63" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AK63" s="1">
@@ -8599,10 +8766,13 @@
         <v>70</v>
       </c>
       <c r="AM63" s="9">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="AN63" s="1"/>
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="AN63" s="1">
+        <f t="shared" si="6"/>
+        <v>12.66</v>
+      </c>
       <c r="AO63" s="1"/>
       <c r="AP63" s="1"/>
       <c r="AQ63" s="1"/>
@@ -8646,30 +8816,30 @@
         <v>161</v>
       </c>
       <c r="L64" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>3</v>
       </c>
       <c r="M64" s="1"/>
       <c r="N64" s="1"/>
       <c r="O64" s="1"/>
       <c r="P64" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>32.799999999999997</v>
       </c>
       <c r="Q64" s="5"/>
       <c r="R64" s="5"/>
       <c r="S64" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="T64" s="1">
-        <f t="shared" si="20"/>
-        <v>32.134146341463421</v>
-      </c>
-      <c r="U64" s="1">
         <f t="shared" si="21"/>
         <v>32.134146341463421</v>
       </c>
+      <c r="U64" s="1">
+        <f t="shared" si="22"/>
+        <v>32.134146341463421</v>
+      </c>
       <c r="V64" s="1">
         <v>25.4</v>
       </c>
@@ -8704,18 +8874,18 @@
         <v>77</v>
       </c>
       <c r="AG64" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AH64" s="7">
         <v>12</v>
       </c>
       <c r="AI64" s="9">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AJ64" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AK64" s="1">
@@ -8725,10 +8895,13 @@
         <v>70</v>
       </c>
       <c r="AM64" s="9">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="AN64" s="1"/>
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="AN64" s="1">
+        <f t="shared" si="6"/>
+        <v>9.8399999999999981</v>
+      </c>
       <c r="AO64" s="1"/>
       <c r="AP64" s="1"/>
       <c r="AQ64" s="1"/>
@@ -8772,33 +8945,33 @@
         <v>53</v>
       </c>
       <c r="L65" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>3</v>
       </c>
       <c r="M65" s="1"/>
       <c r="N65" s="1"/>
       <c r="O65" s="1"/>
       <c r="P65" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>11.2</v>
       </c>
       <c r="Q65" s="5"/>
       <c r="R65" s="5">
-        <f t="shared" ref="R65:R66" si="22">IF(14*P65-F65+P65*$R$1&lt;0,0,14*P65-F65+P65*$R$1)</f>
+        <f t="shared" ref="R65:R66" si="23">IF(14*P65-F65+P65*$R$1&lt;0,0,14*P65-F65+P65*$R$1)</f>
         <v>35.239999999999981</v>
       </c>
       <c r="S65" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="T65" s="1">
-        <f t="shared" si="20"/>
-        <v>12.053571428571429</v>
-      </c>
-      <c r="U65" s="1">
         <f t="shared" si="21"/>
         <v>12.053571428571429</v>
       </c>
+      <c r="U65" s="1">
+        <f t="shared" si="22"/>
+        <v>12.053571428571429</v>
+      </c>
       <c r="V65" s="1">
         <v>3.8</v>
       </c>
@@ -8831,18 +9004,18 @@
       </c>
       <c r="AF65" s="1"/>
       <c r="AG65" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>10.571999999999994</v>
       </c>
       <c r="AH65" s="7">
         <v>14</v>
       </c>
       <c r="AI65" s="9">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AJ65" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AK65" s="1">
@@ -8852,10 +9025,13 @@
         <v>70</v>
       </c>
       <c r="AM65" s="9">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="AN65" s="1"/>
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="AN65" s="1">
+        <f t="shared" si="6"/>
+        <v>3.36</v>
+      </c>
       <c r="AO65" s="1"/>
       <c r="AP65" s="1"/>
       <c r="AQ65" s="1"/>
@@ -8895,33 +9071,33 @@
         <v>65</v>
       </c>
       <c r="L66" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>3</v>
       </c>
       <c r="M66" s="1"/>
       <c r="N66" s="1"/>
       <c r="O66" s="1"/>
       <c r="P66" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>13.6</v>
       </c>
       <c r="Q66" s="5">
         <v>90.4</v>
       </c>
       <c r="R66" s="5">
+        <f t="shared" si="23"/>
+        <v>106.72</v>
+      </c>
+      <c r="S66" s="5">
+        <f t="shared" si="14"/>
+        <v>84</v>
+      </c>
+      <c r="T66" s="1">
+        <f t="shared" si="21"/>
+        <v>13.529411764705882</v>
+      </c>
+      <c r="U66" s="1">
         <f t="shared" si="22"/>
-        <v>106.72</v>
-      </c>
-      <c r="S66" s="5">
-        <f t="shared" si="13"/>
-        <v>84</v>
-      </c>
-      <c r="T66" s="1">
-        <f t="shared" si="20"/>
-        <v>13.529411764705882</v>
-      </c>
-      <c r="U66" s="1">
-        <f t="shared" si="21"/>
         <v>7.3529411764705888</v>
       </c>
       <c r="V66" s="1">
@@ -8958,18 +9134,18 @@
         <v>163</v>
       </c>
       <c r="AG66" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>23.478400000000001</v>
       </c>
       <c r="AH66" s="7">
         <v>6</v>
       </c>
       <c r="AI66" s="9">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>14</v>
       </c>
       <c r="AJ66" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>18.48</v>
       </c>
       <c r="AK66" s="1">
@@ -8979,10 +9155,13 @@
         <v>140</v>
       </c>
       <c r="AM66" s="9">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0.1</v>
       </c>
-      <c r="AN66" s="1"/>
+      <c r="AN66" s="1">
+        <f t="shared" si="6"/>
+        <v>2.992</v>
+      </c>
       <c r="AO66" s="1"/>
       <c r="AP66" s="1"/>
       <c r="AQ66" s="1"/>
@@ -9026,30 +9205,30 @@
         <v>285</v>
       </c>
       <c r="L67" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="M67" s="1"/>
       <c r="N67" s="1"/>
       <c r="O67" s="1"/>
       <c r="P67" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>57</v>
       </c>
       <c r="Q67" s="5"/>
       <c r="R67" s="5"/>
       <c r="S67" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="T67" s="1">
-        <f t="shared" si="20"/>
-        <v>16.701754385964911</v>
-      </c>
-      <c r="U67" s="1">
         <f t="shared" si="21"/>
         <v>16.701754385964911</v>
       </c>
+      <c r="U67" s="1">
+        <f t="shared" si="22"/>
+        <v>16.701754385964911</v>
+      </c>
       <c r="V67" s="1">
         <v>76.8</v>
       </c>
@@ -9082,18 +9261,18 @@
       </c>
       <c r="AF67" s="1"/>
       <c r="AG67" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AH67" s="7">
         <v>12</v>
       </c>
       <c r="AI67" s="9">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AJ67" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AK67" s="1">
@@ -9103,10 +9282,13 @@
         <v>70</v>
       </c>
       <c r="AM67" s="9">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="AN67" s="1"/>
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="AN67" s="1">
+        <f t="shared" si="6"/>
+        <v>14.25</v>
+      </c>
       <c r="AO67" s="1"/>
       <c r="AP67" s="1"/>
       <c r="AQ67" s="1"/>
@@ -9151,30 +9333,30 @@
         <v>278</v>
       </c>
       <c r="L68" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>2</v>
       </c>
       <c r="M68" s="1"/>
       <c r="N68" s="1"/>
       <c r="O68" s="1"/>
       <c r="P68" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>56</v>
       </c>
       <c r="Q68" s="5"/>
       <c r="R68" s="5"/>
       <c r="S68" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="T68" s="1">
-        <f t="shared" si="20"/>
-        <v>19.660714285714285</v>
-      </c>
-      <c r="U68" s="1">
         <f t="shared" si="21"/>
         <v>19.660714285714285</v>
       </c>
+      <c r="U68" s="1">
+        <f t="shared" si="22"/>
+        <v>19.660714285714285</v>
+      </c>
       <c r="V68" s="1">
         <v>62.8</v>
       </c>
@@ -9207,18 +9389,18 @@
       </c>
       <c r="AF68" s="1"/>
       <c r="AG68" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AH68" s="7">
         <v>12</v>
       </c>
       <c r="AI68" s="9">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AJ68" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AK68" s="1">
@@ -9228,10 +9410,13 @@
         <v>70</v>
       </c>
       <c r="AM68" s="9">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="AN68" s="1"/>
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="AN68" s="1">
+        <f t="shared" si="6"/>
+        <v>14</v>
+      </c>
       <c r="AO68" s="1"/>
       <c r="AP68" s="1"/>
       <c r="AQ68" s="1"/>
@@ -9273,14 +9458,14 @@
         <v>55</v>
       </c>
       <c r="L69" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>2</v>
       </c>
       <c r="M69" s="1"/>
       <c r="N69" s="1"/>
       <c r="O69" s="1"/>
       <c r="P69" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>11.4</v>
       </c>
       <c r="Q69" s="5">
@@ -9291,15 +9476,15 @@
         <v>111.20000000000002</v>
       </c>
       <c r="S69" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>84</v>
       </c>
       <c r="T69" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>10.614035087719298</v>
       </c>
       <c r="U69" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>3.2456140350877192</v>
       </c>
       <c r="V69" s="1">
@@ -9334,18 +9519,18 @@
       </c>
       <c r="AF69" s="1"/>
       <c r="AG69" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>22.240000000000006</v>
       </c>
       <c r="AH69" s="7">
         <v>6</v>
       </c>
       <c r="AI69" s="9">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>14</v>
       </c>
       <c r="AJ69" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>16.8</v>
       </c>
       <c r="AK69" s="1">
@@ -9355,10 +9540,13 @@
         <v>140</v>
       </c>
       <c r="AM69" s="9">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0.1</v>
       </c>
-      <c r="AN69" s="1"/>
+      <c r="AN69" s="1">
+        <f t="shared" si="6"/>
+        <v>2.2800000000000002</v>
+      </c>
       <c r="AO69" s="1"/>
       <c r="AP69" s="1"/>
       <c r="AQ69" s="1"/>
@@ -9400,31 +9588,31 @@
         <v>56</v>
       </c>
       <c r="L70" s="1">
-        <f t="shared" ref="L70:L74" si="23">E70-K70</f>
+        <f t="shared" ref="L70:L74" si="24">E70-K70</f>
         <v>-5</v>
       </c>
       <c r="M70" s="1"/>
       <c r="N70" s="1"/>
       <c r="O70" s="1"/>
       <c r="P70" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>10.199999999999999</v>
       </c>
       <c r="Q70" s="5"/>
       <c r="R70" s="5">
-        <f t="shared" ref="R70:R71" si="24">IF(14*P70-F70+P70*$R$1&lt;0,0,14*P70-F70+P70*$R$1)</f>
+        <f t="shared" ref="R70:R71" si="25">IF(14*P70-F70+P70*$R$1&lt;0,0,14*P70-F70+P70*$R$1)</f>
         <v>5.0399999999999814</v>
       </c>
       <c r="S70" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="T70" s="1">
-        <f t="shared" ref="T70:T74" si="25">(F70+S70)/P70</f>
+        <f t="shared" ref="T70:T74" si="26">(F70+S70)/P70</f>
         <v>14.705882352941178</v>
       </c>
       <c r="U70" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>14.705882352941178</v>
       </c>
       <c r="V70" s="1">
@@ -9459,18 +9647,18 @@
       </c>
       <c r="AF70" s="1"/>
       <c r="AG70" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1.1591999999999958</v>
       </c>
       <c r="AH70" s="7">
         <v>6</v>
       </c>
       <c r="AI70" s="9">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AJ70" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AK70" s="1">
@@ -9480,10 +9668,13 @@
         <v>140</v>
       </c>
       <c r="AM70" s="9">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="AN70" s="1"/>
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="AN70" s="1">
+        <f t="shared" si="6"/>
+        <v>2.3460000000000001</v>
+      </c>
       <c r="AO70" s="1"/>
       <c r="AP70" s="1"/>
       <c r="AQ70" s="1"/>
@@ -9523,33 +9714,33 @@
         <v>128</v>
       </c>
       <c r="L71" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>8</v>
       </c>
       <c r="M71" s="1"/>
       <c r="N71" s="1"/>
       <c r="O71" s="1"/>
       <c r="P71" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>27.2</v>
       </c>
       <c r="Q71" s="5">
         <v>74.800000000000011</v>
       </c>
       <c r="R71" s="5">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>107.44000000000001</v>
       </c>
       <c r="S71" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>84</v>
       </c>
       <c r="T71" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>14.338235294117647</v>
       </c>
       <c r="U71" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>11.25</v>
       </c>
       <c r="V71" s="1">
@@ -9586,18 +9777,18 @@
         <v>163</v>
       </c>
       <c r="AG71" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>24.711200000000005</v>
       </c>
       <c r="AH71" s="7">
         <v>6</v>
       </c>
       <c r="AI71" s="9">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>14</v>
       </c>
       <c r="AJ71" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>19.32</v>
       </c>
       <c r="AK71" s="1">
@@ -9607,10 +9798,13 @@
         <v>140</v>
       </c>
       <c r="AM71" s="9">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0.1</v>
       </c>
-      <c r="AN71" s="1"/>
+      <c r="AN71" s="1">
+        <f t="shared" ref="AN71:AN74" si="27">P71*G71</f>
+        <v>6.2560000000000002</v>
+      </c>
       <c r="AO71" s="1"/>
       <c r="AP71" s="1"/>
       <c r="AQ71" s="1"/>
@@ -9654,28 +9848,28 @@
         <v>50.1</v>
       </c>
       <c r="L72" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>1.1999999999999957</v>
       </c>
       <c r="M72" s="1"/>
       <c r="N72" s="1"/>
       <c r="O72" s="1"/>
       <c r="P72" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>10.26</v>
       </c>
       <c r="Q72" s="5"/>
       <c r="R72" s="5"/>
       <c r="S72" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="T72" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>35.789473684210527</v>
       </c>
       <c r="U72" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>35.789473684210527</v>
       </c>
       <c r="V72" s="1">
@@ -9712,18 +9906,18 @@
         <v>77</v>
       </c>
       <c r="AG72" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AH72" s="7">
         <v>2.7</v>
       </c>
       <c r="AI72" s="9">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AJ72" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AK72" s="1">
@@ -9733,10 +9927,13 @@
         <v>126</v>
       </c>
       <c r="AM72" s="9">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="AN72" s="1"/>
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="AN72" s="1">
+        <f t="shared" si="27"/>
+        <v>10.26</v>
+      </c>
       <c r="AO72" s="1"/>
       <c r="AP72" s="1"/>
       <c r="AQ72" s="1"/>
@@ -9781,14 +9978,14 @@
         <v>375</v>
       </c>
       <c r="L73" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>-60</v>
       </c>
       <c r="M73" s="1"/>
       <c r="N73" s="1"/>
       <c r="O73" s="1"/>
       <c r="P73" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>63</v>
       </c>
       <c r="Q73" s="5">
@@ -9799,15 +9996,15 @@
         <v>653.5</v>
       </c>
       <c r="S73" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>660</v>
       </c>
       <c r="T73" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>11.103174603174603</v>
       </c>
       <c r="U73" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0.62698412698412698</v>
       </c>
       <c r="V73" s="1">
@@ -9842,18 +10039,18 @@
       </c>
       <c r="AF73" s="1"/>
       <c r="AG73" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>653.5</v>
       </c>
       <c r="AH73" s="7">
         <v>5</v>
       </c>
       <c r="AI73" s="9">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>132</v>
       </c>
       <c r="AJ73" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>660</v>
       </c>
       <c r="AK73" s="1">
@@ -9863,10 +10060,13 @@
         <v>84</v>
       </c>
       <c r="AM73" s="9">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>1.5714285714285714</v>
       </c>
-      <c r="AN73" s="1"/>
+      <c r="AN73" s="1">
+        <f t="shared" si="27"/>
+        <v>63</v>
+      </c>
       <c r="AO73" s="1"/>
       <c r="AP73" s="1"/>
       <c r="AQ73" s="1"/>
@@ -9906,25 +10106,25 @@
         <v>5</v>
       </c>
       <c r="L74" s="14">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>-5</v>
       </c>
       <c r="M74" s="14"/>
       <c r="N74" s="14"/>
       <c r="O74" s="14"/>
       <c r="P74" s="14">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="Q74" s="16"/>
       <c r="R74" s="16"/>
       <c r="S74" s="16"/>
       <c r="T74" s="14" t="e">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U74" s="14" t="e">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V74" s="14">
@@ -9965,7 +10165,10 @@
       <c r="AK74" s="14"/>
       <c r="AL74" s="14"/>
       <c r="AM74" s="17"/>
-      <c r="AN74" s="1"/>
+      <c r="AN74" s="1">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
       <c r="AO74" s="1"/>
       <c r="AP74" s="1"/>
       <c r="AQ74" s="1"/>
